--- a/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
+++ b/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD8F7DB8-F338-4D17-B5B7-BD9F4B557C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1166BCE5-668C-4AB7-BE9F-C876EBBD9B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
     <sheet name="標音字庫" sheetId="129" r:id="rId2"/>
     <sheet name="缺字表" sheetId="128" r:id="rId3"/>
-    <sheet name="漢字注音" sheetId="9" r:id="rId4"/>
-    <sheet name="缺字表 (範例)" sheetId="110" r:id="rId5"/>
-    <sheet name="標音字庫 (範例)" sheetId="121" r:id="rId6"/>
-    <sheet name="漢字注音 (範例)" sheetId="120" r:id="rId7"/>
+    <sheet name="人工標音字庫" sheetId="130" r:id="rId4"/>
+    <sheet name="漢字注音" sheetId="9" r:id="rId5"/>
+    <sheet name="缺字表 (範例)" sheetId="110" r:id="rId6"/>
+    <sheet name="標音字庫 (範例)" sheetId="121" r:id="rId7"/>
+    <sheet name="漢字注音 (範例)" sheetId="120" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="FILE_NAME">env!$C$5</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2760" uniqueCount="1306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="1311">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4439,6 +4440,25 @@
   <si>
     <t>https://i2.kknews.cc/MXoThPNJkoeAOEZxR8RqnqCwNCYU74wh_Q/0.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台語音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>校正音標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>座標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx</t>
   </si>
 </sst>
 </file>
@@ -6804,7 +6824,9 @@
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>1310</v>
+      </c>
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="4" t="s">
@@ -6966,16 +6988,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>1306</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>1307</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>1308</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7761,16 +7783,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>1306</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>1307</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>1308</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>1309</v>
       </c>
     </row>
   </sheetData>
@@ -7780,6 +7802,31 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97FE190-453D-4F43-B6DA-20896ABFE75A}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B653E275-5A31-466A-99DB-0BBFEE8A78C6}">
   <dimension ref="A1:V2002"/>
   <sheetFormatPr defaultRowHeight="39"/>
@@ -48365,7 +48412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2180A89-0265-4346-97D5-5D16606F5B0F}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -48529,7 +48576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD15F3BA-C880-4104-B992-B0FF90EEBE97}">
   <dimension ref="A1:E238"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -52587,7 +52634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C93001D-D880-46B9-9D80-7A0F5AA84ACC}">
   <dimension ref="A1:V241"/>
   <sheetFormatPr defaultRowHeight="39"/>

--- a/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
+++ b/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1166BCE5-668C-4AB7-BE9F-C876EBBD9B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3AF945-792E-4216-9CED-A7810B562435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2765" uniqueCount="1311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="1310">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4013,9 +4013,6 @@
   </si>
   <si>
     <t>經</t>
-  </si>
-  <si>
-    <t>．</t>
   </si>
   <si>
     <t>小</t>
@@ -4438,10 +4435,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://i2.kknews.cc/MXoThPNJkoeAOEZxR8RqnqCwNCYU74wh_Q/0.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>漢字</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4458,7 +4451,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Si1-King1.jpg</t>
+  </si>
+  <si>
     <t>【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6825,7 +6822,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -6833,7 +6830,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="7" spans="2:4">
@@ -6841,7 +6838,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="D7" s="47"/>
     </row>
@@ -6974,9 +6971,6 @@
       <formula1>" ,十五音, 雅俗通,方音符號,注音二式,台語音標, 白話字, 台羅拼音,閩拼調號, 閩拼調符"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{A0A7310A-FFA3-48F8-92C5-B03F06FF3EF5}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6988,16 +6982,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C1" t="s">
         <v>1306</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1307</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7030,49 +7024,49 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B4" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C4" t="s">
         <v>499</v>
       </c>
       <c r="D4" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B5" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C5" t="s">
         <v>499</v>
       </c>
       <c r="D5" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B6" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C6" t="s">
         <v>499</v>
       </c>
       <c r="D6" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B7" t="s">
         <v>312</v>
@@ -7081,12 +7075,12 @@
         <v>499</v>
       </c>
       <c r="D7" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B8" t="s">
         <v>416</v>
@@ -7095,35 +7089,35 @@
         <v>499</v>
       </c>
       <c r="D8" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B9" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C9" t="s">
         <v>499</v>
       </c>
       <c r="D9" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B10" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C10" t="s">
         <v>499</v>
       </c>
       <c r="D10" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7137,35 +7131,35 @@
         <v>499</v>
       </c>
       <c r="D11" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B12" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C12" t="s">
         <v>499</v>
       </c>
       <c r="D12" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B13" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C13" t="s">
         <v>499</v>
       </c>
       <c r="D13" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -7179,40 +7173,40 @@
         <v>499</v>
       </c>
       <c r="D14" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B15" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C15" t="s">
         <v>499</v>
       </c>
       <c r="D15" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B16" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C16" t="s">
         <v>499</v>
       </c>
       <c r="D16" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B17" t="s">
         <v>467</v>
@@ -7221,26 +7215,26 @@
         <v>499</v>
       </c>
       <c r="D17" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B18" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C18" t="s">
         <v>499</v>
       </c>
       <c r="D18" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B19" t="s">
         <v>403</v>
@@ -7249,12 +7243,12 @@
         <v>499</v>
       </c>
       <c r="D19" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B20" t="s">
         <v>62</v>
@@ -7263,40 +7257,40 @@
         <v>499</v>
       </c>
       <c r="D20" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B21" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C21" t="s">
         <v>499</v>
       </c>
       <c r="D21" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B22" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C22" t="s">
         <v>499</v>
       </c>
       <c r="D22" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B23" t="s">
         <v>394</v>
@@ -7305,7 +7299,7 @@
         <v>499</v>
       </c>
       <c r="D23" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -7319,21 +7313,21 @@
         <v>499</v>
       </c>
       <c r="D24" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B25" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C25" t="s">
         <v>499</v>
       </c>
       <c r="D25" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -7347,26 +7341,26 @@
         <v>499</v>
       </c>
       <c r="D26" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B27" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C27" t="s">
         <v>499</v>
       </c>
       <c r="D27" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B28" t="s">
         <v>53</v>
@@ -7375,21 +7369,21 @@
         <v>499</v>
       </c>
       <c r="D28" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B29" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C29" t="s">
         <v>499</v>
       </c>
       <c r="D29" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -7403,26 +7397,26 @@
         <v>499</v>
       </c>
       <c r="D30" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B31" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C31" t="s">
         <v>499</v>
       </c>
       <c r="D31" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B32" t="s">
         <v>307</v>
@@ -7436,10 +7430,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B33" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C33" t="s">
         <v>499</v>
@@ -7450,24 +7444,24 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B34" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C34" t="s">
         <v>499</v>
       </c>
       <c r="D34" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B35" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C35" t="s">
         <v>499</v>
@@ -7478,7 +7472,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
@@ -7487,7 +7481,7 @@
         <v>499</v>
       </c>
       <c r="D36" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -7501,7 +7495,7 @@
         <v>499</v>
       </c>
       <c r="D37" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -7515,15 +7509,15 @@
         <v>499</v>
       </c>
       <c r="D38" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B39" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C39" t="s">
         <v>499</v>
@@ -7543,7 +7537,7 @@
         <v>499</v>
       </c>
       <c r="D40" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -7557,7 +7551,7 @@
         <v>499</v>
       </c>
       <c r="D41" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -7571,26 +7565,26 @@
         <v>499</v>
       </c>
       <c r="D42" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B43" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C43" t="s">
         <v>499</v>
       </c>
       <c r="D43" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B44" t="s">
         <v>440</v>
@@ -7599,7 +7593,7 @@
         <v>499</v>
       </c>
       <c r="D44" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -7613,15 +7607,15 @@
         <v>499</v>
       </c>
       <c r="D45" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B46" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C46" t="s">
         <v>499</v>
@@ -7632,7 +7626,7 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B47" t="s">
         <v>443</v>
@@ -7641,7 +7635,7 @@
         <v>499</v>
       </c>
       <c r="D47" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -7655,49 +7649,49 @@
         <v>499</v>
       </c>
       <c r="D48" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B49" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C49" t="s">
         <v>499</v>
       </c>
       <c r="D49" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B50" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C50" t="s">
         <v>499</v>
       </c>
       <c r="D50" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B51" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C51" t="s">
         <v>499</v>
       </c>
       <c r="D51" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -7711,7 +7705,7 @@
         <v>499</v>
       </c>
       <c r="D52" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -7719,41 +7713,41 @@
         <v>251</v>
       </c>
       <c r="B53" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C53" t="s">
         <v>499</v>
       </c>
       <c r="D53" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B54" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C54" t="s">
         <v>499</v>
       </c>
       <c r="D54" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B55" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C55" t="s">
         <v>499</v>
       </c>
       <c r="D55" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -7767,7 +7761,7 @@
         <v>499</v>
       </c>
       <c r="D56" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
   </sheetData>
@@ -7783,16 +7777,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C1" t="s">
         <v>1306</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1307</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1309</v>
       </c>
     </row>
   </sheetData>
@@ -7808,16 +7802,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>1304</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>1305</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>1306</v>
       </c>
       <c r="D1" t="s">
-        <v>498</v>
+        <v>1307</v>
       </c>
     </row>
   </sheetData>
@@ -7914,7 +7908,7 @@
       <c r="R3" s="52"/>
       <c r="T3" s="16"/>
       <c r="V3" s="54" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
@@ -7928,14 +7922,14 @@
       </c>
       <c r="G4" s="50"/>
       <c r="H4" s="50" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="I4" s="50" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="J4" s="50"/>
       <c r="K4" s="50" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="L4" s="50" t="s">
         <v>312</v>
@@ -7962,26 +7956,22 @@
       <c r="F5" s="39" t="s">
         <v>1168</v>
       </c>
-      <c r="G5" s="39" t="s">
+      <c r="G5" s="39"/>
+      <c r="H5" s="39" t="s">
         <v>1169</v>
       </c>
-      <c r="H5" s="39" t="s">
+      <c r="I5" s="39" t="s">
         <v>1170</v>
       </c>
-      <c r="I5" s="39" t="s">
+      <c r="J5" s="39"/>
+      <c r="K5" s="39" t="s">
         <v>1171</v>
       </c>
-      <c r="J5" s="39" t="s">
-        <v>1169</v>
-      </c>
-      <c r="K5" s="39" t="s">
+      <c r="L5" s="39" t="s">
         <v>1172</v>
       </c>
-      <c r="L5" s="39" t="s">
+      <c r="M5" s="39" t="s">
         <v>1173</v>
-      </c>
-      <c r="M5" s="39" t="s">
-        <v>1174</v>
       </c>
       <c r="N5" s="39" t="str">
         <f>CHAR(10)</f>
@@ -8003,21 +7993,21 @@
         <v>331</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="G6" s="51"/>
       <c r="H6" s="51" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="I6" s="51" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="J6" s="51"/>
       <c r="K6" s="51" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="L6" s="51" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="M6" s="51"/>
       <c r="N6" s="51"/>
@@ -8058,23 +8048,23 @@
         <v>416</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G8" s="50" t="s">
         <v>312</v>
       </c>
       <c r="H8" s="50"/>
       <c r="I8" s="50" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="J8" s="50" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="K8" s="50" t="s">
         <v>338</v>
       </c>
       <c r="L8" s="50" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="M8" s="50"/>
       <c r="N8" s="50"/>
@@ -8091,31 +8081,31 @@
         <v>2</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="F9" s="39" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G9" s="39" t="s">
         <v>1172</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>1173</v>
       </c>
       <c r="H9" s="39" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="39" t="s">
+        <v>1175</v>
+      </c>
+      <c r="J9" s="39" t="s">
         <v>1176</v>
-      </c>
-      <c r="J9" s="39" t="s">
-        <v>1177</v>
       </c>
       <c r="K9" s="39" t="s">
         <v>108</v>
       </c>
       <c r="L9" s="39" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="M9" s="39" t="s">
         <v>30</v>
@@ -8142,23 +8132,23 @@
         <v>416</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H10" s="51"/>
       <c r="I10" s="51" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="J10" s="51" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="K10" s="51" t="s">
         <v>338</v>
       </c>
       <c r="L10" s="51" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="M10" s="51"/>
       <c r="N10" s="51"/>
@@ -8192,23 +8182,23 @@
     <row r="12" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="17"/>
       <c r="D12" s="50" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>411</v>
       </c>
       <c r="F12" s="50" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G12" s="50" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H12" s="50"/>
       <c r="I12" s="50" t="s">
         <v>467</v>
       </c>
       <c r="J12" s="50" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="K12" s="50" t="s">
         <v>403</v>
@@ -8231,31 +8221,31 @@
         <v>3</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E13" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="39" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G13" s="39" t="s">
         <v>1180</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>1181</v>
       </c>
       <c r="H13" s="39" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="39" t="s">
+        <v>1181</v>
+      </c>
+      <c r="J13" s="39" t="s">
         <v>1182</v>
       </c>
-      <c r="J13" s="39" t="s">
+      <c r="K13" s="39" t="s">
         <v>1183</v>
       </c>
-      <c r="K13" s="39" t="s">
+      <c r="L13" s="39" t="s">
         <v>1184</v>
-      </c>
-      <c r="L13" s="39" t="s">
-        <v>1185</v>
       </c>
       <c r="M13" s="39" t="s">
         <v>30</v>
@@ -8275,23 +8265,23 @@
     <row r="14" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="21"/>
       <c r="D14" s="51" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E14" s="51" t="s">
         <v>411</v>
       </c>
       <c r="F14" s="51" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G14" s="51" t="s">
         <v>1287</v>
-      </c>
-      <c r="G14" s="51" t="s">
-        <v>1288</v>
       </c>
       <c r="H14" s="51"/>
       <c r="I14" s="51" t="s">
+        <v>1288</v>
+      </c>
+      <c r="J14" s="51" t="s">
         <v>1289</v>
-      </c>
-      <c r="J14" s="51" t="s">
-        <v>1290</v>
       </c>
       <c r="K14" s="51" t="s">
         <v>403</v>
@@ -8340,11 +8330,11 @@
         <v>467</v>
       </c>
       <c r="G16" s="50" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H16" s="50"/>
       <c r="I16" s="50" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J16" s="50" t="s">
         <v>394</v>
@@ -8353,7 +8343,7 @@
         <v>53</v>
       </c>
       <c r="L16" s="50" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="M16" s="50"/>
       <c r="N16" s="50"/>
@@ -8370,31 +8360,31 @@
         <v>4</v>
       </c>
       <c r="D17" s="39" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E17" s="39" t="s">
         <v>1184</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="F17" s="39" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G17" s="39" t="s">
         <v>1185</v>
-      </c>
-      <c r="F17" s="39" t="s">
-        <v>1182</v>
-      </c>
-      <c r="G17" s="39" t="s">
-        <v>1186</v>
       </c>
       <c r="H17" s="39" t="s">
         <v>23</v>
       </c>
       <c r="I17" s="39" t="s">
+        <v>1186</v>
+      </c>
+      <c r="J17" s="39" t="s">
         <v>1187</v>
-      </c>
-      <c r="J17" s="39" t="s">
-        <v>1188</v>
       </c>
       <c r="K17" s="39" t="s">
         <v>33</v>
       </c>
       <c r="L17" s="39" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="M17" s="39" t="s">
         <v>30</v>
@@ -8420,14 +8410,14 @@
         <v>62</v>
       </c>
       <c r="F18" s="51" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="G18" s="51" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="H18" s="51"/>
       <c r="I18" s="51" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J18" s="51" t="s">
         <v>429</v>
@@ -8436,7 +8426,7 @@
         <v>53</v>
       </c>
       <c r="L18" s="51" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="M18" s="51"/>
       <c r="N18" s="51"/>
@@ -8478,20 +8468,20 @@
         <v>338</v>
       </c>
       <c r="F20" s="50" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G20" s="50" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H20" s="50"/>
       <c r="I20" s="50" t="s">
         <v>53</v>
       </c>
       <c r="J20" s="50" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="K20" s="50" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="L20" s="50" t="s">
         <v>400</v>
@@ -8517,22 +8507,22 @@
         <v>108</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H21" s="39" t="s">
         <v>23</v>
       </c>
       <c r="I21" s="39" t="s">
+        <v>1190</v>
+      </c>
+      <c r="J21" s="39" t="s">
+        <v>1178</v>
+      </c>
+      <c r="K21" s="39" t="s">
         <v>1191</v>
-      </c>
-      <c r="J21" s="39" t="s">
-        <v>1179</v>
-      </c>
-      <c r="K21" s="39" t="s">
-        <v>1192</v>
       </c>
       <c r="L21" s="39" t="s">
         <v>185</v>
@@ -8555,26 +8545,26 @@
     <row r="22" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="21"/>
       <c r="D22" s="51" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E22" s="51" t="s">
         <v>338</v>
       </c>
       <c r="F22" s="51" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="G22" s="51" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="H22" s="51"/>
       <c r="I22" s="51" t="s">
         <v>53</v>
       </c>
       <c r="J22" s="51" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="K22" s="51" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="L22" s="51" t="s">
         <v>400</v>
@@ -8617,23 +8607,23 @@
         <v>416</v>
       </c>
       <c r="F24" s="50" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G24" s="50" t="s">
         <v>312</v>
       </c>
       <c r="H24" s="50"/>
       <c r="I24" s="50" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="J24" s="50" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="K24" s="50" t="s">
         <v>338</v>
       </c>
       <c r="L24" s="50" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="M24" s="50"/>
       <c r="N24" s="50"/>
@@ -8650,31 +8640,31 @@
         <v>6</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="F25" s="39" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G25" s="39" t="s">
         <v>1172</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>1173</v>
       </c>
       <c r="H25" s="39" t="s">
         <v>23</v>
       </c>
       <c r="I25" s="39" t="s">
+        <v>1175</v>
+      </c>
+      <c r="J25" s="39" t="s">
         <v>1176</v>
-      </c>
-      <c r="J25" s="39" t="s">
-        <v>1177</v>
       </c>
       <c r="K25" s="39" t="s">
         <v>108</v>
       </c>
       <c r="L25" s="39" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="M25" s="39" t="s">
         <v>30</v>
@@ -8700,23 +8690,23 @@
         <v>416</v>
       </c>
       <c r="F26" s="51" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G26" s="51" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H26" s="51"/>
       <c r="I26" s="51" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="J26" s="51" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="K26" s="51" t="s">
         <v>338</v>
       </c>
       <c r="L26" s="51" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="M26" s="51"/>
       <c r="N26" s="51"/>
@@ -8750,29 +8740,29 @@
     <row r="28" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B28" s="17"/>
       <c r="D28" s="50" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E28" s="50" t="s">
         <v>411</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G28" s="50" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H28" s="50"/>
       <c r="I28" s="50" t="s">
         <v>307</v>
       </c>
       <c r="J28" s="50" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K28" s="50" t="s">
         <v>1254</v>
       </c>
-      <c r="K28" s="50" t="s">
-        <v>1255</v>
-      </c>
       <c r="L28" s="50" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="M28" s="50"/>
       <c r="N28" s="50"/>
@@ -8790,31 +8780,31 @@
         <v>7</v>
       </c>
       <c r="D29" s="39" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E29" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F29" s="39" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G29" s="39" t="s">
         <v>1180</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>1181</v>
       </c>
       <c r="H29" s="39" t="s">
         <v>23</v>
       </c>
       <c r="I29" s="39" t="s">
+        <v>1193</v>
+      </c>
+      <c r="J29" s="39" t="s">
         <v>1194</v>
       </c>
-      <c r="J29" s="39" t="s">
+      <c r="K29" s="39" t="s">
         <v>1195</v>
       </c>
-      <c r="K29" s="39" t="s">
+      <c r="L29" s="39" t="s">
         <v>1196</v>
-      </c>
-      <c r="L29" s="39" t="s">
-        <v>1197</v>
       </c>
       <c r="M29" s="39" t="s">
         <v>30</v>
@@ -8835,29 +8825,29 @@
     <row r="30" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B30" s="21"/>
       <c r="D30" s="51" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E30" s="51" t="s">
         <v>411</v>
       </c>
       <c r="F30" s="51" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G30" s="51" t="s">
         <v>1287</v>
-      </c>
-      <c r="G30" s="51" t="s">
-        <v>1288</v>
       </c>
       <c r="H30" s="51"/>
       <c r="I30" s="51" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J30" s="51" t="s">
+        <v>1253</v>
+      </c>
+      <c r="K30" s="51" t="s">
         <v>1294</v>
       </c>
-      <c r="J30" s="51" t="s">
-        <v>1254</v>
-      </c>
-      <c r="K30" s="51" t="s">
-        <v>1295</v>
-      </c>
       <c r="L30" s="51" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="M30" s="51"/>
       <c r="N30" s="51"/>
@@ -8901,7 +8891,7 @@
         <v>387</v>
       </c>
       <c r="G32" s="50" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H32" s="50"/>
       <c r="I32" s="50" t="s">
@@ -8920,7 +8910,7 @@
         <v>53</v>
       </c>
       <c r="N32" s="50" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="O32" s="50"/>
       <c r="P32" s="50"/>
@@ -8936,7 +8926,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E33" s="39" t="s">
         <v>279</v>
@@ -8945,7 +8935,7 @@
         <v>168</v>
       </c>
       <c r="G33" s="39" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="H33" s="39" t="s">
         <v>23</v>
@@ -8966,7 +8956,7 @@
         <v>33</v>
       </c>
       <c r="N33" s="39" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="O33" s="39" t="s">
         <v>30</v>
@@ -8987,17 +8977,17 @@
         <v>53</v>
       </c>
       <c r="E34" s="51" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F34" s="51" t="s">
         <v>1296</v>
-      </c>
-      <c r="F34" s="51" t="s">
-        <v>1297</v>
       </c>
       <c r="G34" s="51" t="s">
         <v>356</v>
       </c>
       <c r="H34" s="51"/>
       <c r="I34" s="51" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="J34" s="51" t="s">
         <v>305</v>
@@ -9006,13 +8996,13 @@
         <v>53</v>
       </c>
       <c r="L34" s="51" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="M34" s="51" t="s">
         <v>53</v>
       </c>
       <c r="N34" s="51" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="O34" s="51"/>
       <c r="P34" s="51"/>
@@ -9044,7 +9034,7 @@
     <row r="36" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="17"/>
       <c r="D36" s="50" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E36" s="50" t="s">
         <v>411</v>
@@ -9057,13 +9047,13 @@
       </c>
       <c r="H36" s="50"/>
       <c r="I36" s="50" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="J36" s="50" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="K36" s="50" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="L36" s="50" t="s">
         <v>443</v>
@@ -9072,7 +9062,7 @@
         <v>336</v>
       </c>
       <c r="N36" s="50" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="O36" s="50"/>
       <c r="P36" s="50"/>
@@ -9087,13 +9077,13 @@
         <v>9</v>
       </c>
       <c r="D37" s="39" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E37" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F37" s="39" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G37" s="39" t="s">
         <v>262</v>
@@ -9102,22 +9092,22 @@
         <v>23</v>
       </c>
       <c r="I37" s="39" t="s">
+        <v>1179</v>
+      </c>
+      <c r="J37" s="39" t="s">
         <v>1180</v>
       </c>
-      <c r="J37" s="39" t="s">
-        <v>1181</v>
-      </c>
       <c r="K37" s="39" t="s">
+        <v>1201</v>
+      </c>
+      <c r="L37" s="39" t="s">
         <v>1202</v>
-      </c>
-      <c r="L37" s="39" t="s">
-        <v>1203</v>
       </c>
       <c r="M37" s="39" t="s">
         <v>106</v>
       </c>
       <c r="N37" s="39" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="O37" s="39" t="s">
         <v>30</v>
@@ -9135,7 +9125,7 @@
     <row r="38" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="21"/>
       <c r="D38" s="51" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E38" s="51" t="s">
         <v>411</v>
@@ -9148,13 +9138,13 @@
       </c>
       <c r="H38" s="51"/>
       <c r="I38" s="51" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J38" s="51" t="s">
         <v>1287</v>
       </c>
-      <c r="J38" s="51" t="s">
-        <v>1288</v>
-      </c>
       <c r="K38" s="51" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="L38" s="51" t="s">
         <v>443</v>
@@ -9163,7 +9153,7 @@
         <v>336</v>
       </c>
       <c r="N38" s="51" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="O38" s="51"/>
       <c r="P38" s="51"/>
@@ -9201,23 +9191,23 @@
         <v>416</v>
       </c>
       <c r="F40" s="50" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G40" s="50" t="s">
         <v>312</v>
       </c>
       <c r="H40" s="50"/>
       <c r="I40" s="50" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="J40" s="50" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="K40" s="50" t="s">
         <v>338</v>
       </c>
       <c r="L40" s="50" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="M40" s="50"/>
       <c r="N40" s="50"/>
@@ -9234,31 +9224,31 @@
         <v>10</v>
       </c>
       <c r="D41" s="39" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E41" s="39" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="F41" s="39" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G41" s="39" t="s">
         <v>1172</v>
-      </c>
-      <c r="G41" s="39" t="s">
-        <v>1173</v>
       </c>
       <c r="H41" s="39" t="s">
         <v>23</v>
       </c>
       <c r="I41" s="39" t="s">
+        <v>1175</v>
+      </c>
+      <c r="J41" s="39" t="s">
         <v>1176</v>
-      </c>
-      <c r="J41" s="39" t="s">
-        <v>1177</v>
       </c>
       <c r="K41" s="39" t="s">
         <v>108</v>
       </c>
       <c r="L41" s="39" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="M41" s="39" t="s">
         <v>30</v>
@@ -9284,23 +9274,23 @@
         <v>416</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H42" s="51"/>
       <c r="I42" s="51" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="J42" s="51" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="K42" s="51" t="s">
         <v>338</v>
       </c>
       <c r="L42" s="51" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="M42" s="51"/>
       <c r="N42" s="51"/>
@@ -9334,29 +9324,29 @@
     <row r="44" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B44" s="17"/>
       <c r="D44" s="50" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E44" s="50" t="s">
         <v>411</v>
       </c>
       <c r="F44" s="50" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G44" s="50" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H44" s="50"/>
       <c r="I44" s="50" t="s">
         <v>467</v>
       </c>
       <c r="J44" s="50" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="K44" s="50" t="s">
         <v>467</v>
       </c>
       <c r="L44" s="50" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="M44" s="50"/>
       <c r="N44" s="50"/>
@@ -9373,31 +9363,31 @@
         <v>11</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E45" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F45" s="39" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G45" s="39" t="s">
         <v>1180</v>
-      </c>
-      <c r="G45" s="39" t="s">
-        <v>1181</v>
       </c>
       <c r="H45" s="39" t="s">
         <v>23</v>
       </c>
       <c r="I45" s="39" t="s">
+        <v>1181</v>
+      </c>
+      <c r="J45" s="39" t="s">
         <v>1182</v>
       </c>
-      <c r="J45" s="39" t="s">
-        <v>1183</v>
-      </c>
       <c r="K45" s="39" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="L45" s="39" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="M45" s="39" t="s">
         <v>30</v>
@@ -9417,29 +9407,29 @@
     <row r="46" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B46" s="21"/>
       <c r="D46" s="51" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E46" s="51" t="s">
         <v>411</v>
       </c>
       <c r="F46" s="51" t="s">
+        <v>1286</v>
+      </c>
+      <c r="G46" s="51" t="s">
         <v>1287</v>
-      </c>
-      <c r="G46" s="51" t="s">
-        <v>1288</v>
       </c>
       <c r="H46" s="51"/>
       <c r="I46" s="51" t="s">
+        <v>1288</v>
+      </c>
+      <c r="J46" s="51" t="s">
         <v>1289</v>
       </c>
-      <c r="J46" s="51" t="s">
-        <v>1290</v>
-      </c>
       <c r="K46" s="51" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="L46" s="51" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="M46" s="51"/>
       <c r="N46" s="51"/>
@@ -9476,26 +9466,26 @@
         <v>467</v>
       </c>
       <c r="E48" s="50" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F48" s="50" t="s">
         <v>467</v>
       </c>
       <c r="G48" s="50" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="H48" s="50"/>
       <c r="I48" s="50" t="s">
         <v>40</v>
       </c>
       <c r="J48" s="50" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="K48" s="50" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="L48" s="50" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="M48" s="50"/>
       <c r="N48" s="50"/>
@@ -9512,16 +9502,16 @@
         <v>12</v>
       </c>
       <c r="D49" s="39" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E49" s="39" t="s">
         <v>1182</v>
       </c>
-      <c r="E49" s="39" t="s">
-        <v>1183</v>
-      </c>
       <c r="F49" s="39" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G49" s="39" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="H49" s="39" t="s">
         <v>23</v>
@@ -9533,10 +9523,10 @@
         <v>251</v>
       </c>
       <c r="K49" s="39" t="s">
+        <v>1206</v>
+      </c>
+      <c r="L49" s="39" t="s">
         <v>1207</v>
-      </c>
-      <c r="L49" s="39" t="s">
-        <v>1208</v>
       </c>
       <c r="M49" s="39" t="s">
         <v>30</v>
@@ -9556,29 +9546,29 @@
     <row r="50" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B50" s="21"/>
       <c r="D50" s="51" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E50" s="51" t="s">
         <v>1289</v>
       </c>
-      <c r="E50" s="51" t="s">
-        <v>1290</v>
-      </c>
       <c r="F50" s="51" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="G50" s="51" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="H50" s="51"/>
       <c r="I50" s="51" t="s">
+        <v>1301</v>
+      </c>
+      <c r="J50" s="51" t="s">
+        <v>1213</v>
+      </c>
+      <c r="K50" s="51" t="s">
+        <v>1278</v>
+      </c>
+      <c r="L50" s="51" t="s">
         <v>1302</v>
-      </c>
-      <c r="J50" s="51" t="s">
-        <v>1214</v>
-      </c>
-      <c r="K50" s="51" t="s">
-        <v>1279</v>
-      </c>
-      <c r="L50" s="51" t="s">
-        <v>1303</v>
       </c>
       <c r="M50" s="51"/>
       <c r="N50" s="51"/>
@@ -9612,7 +9602,7 @@
     <row r="52" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="17"/>
       <c r="D52" s="50" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E52" s="50" t="s">
         <v>411</v>
@@ -9631,13 +9621,13 @@
         <v>443</v>
       </c>
       <c r="K52" s="50" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="L52" s="50" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="M52" s="50" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="N52" s="50" t="s">
         <v>338</v>
@@ -9657,13 +9647,13 @@
         <v>13</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="E53" s="39" t="s">
         <v>19</v>
       </c>
       <c r="F53" s="39" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G53" s="39" t="s">
         <v>262</v>
@@ -9675,16 +9665,16 @@
         <v>106</v>
       </c>
       <c r="J53" s="39" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K53" s="39" t="s">
         <v>251</v>
       </c>
       <c r="L53" s="39" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M53" s="39" t="s">
         <v>1180</v>
-      </c>
-      <c r="M53" s="39" t="s">
-        <v>1181</v>
       </c>
       <c r="N53" s="39" t="s">
         <v>108</v>
@@ -9707,7 +9697,7 @@
     <row r="54" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="21"/>
       <c r="D54" s="51" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E54" s="51" t="s">
         <v>411</v>
@@ -9726,13 +9716,13 @@
         <v>443</v>
       </c>
       <c r="K54" s="51" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="L54" s="51" t="s">
+        <v>1286</v>
+      </c>
+      <c r="M54" s="51" t="s">
         <v>1287</v>
-      </c>
-      <c r="M54" s="51" t="s">
-        <v>1288</v>
       </c>
       <c r="N54" s="51" t="s">
         <v>338</v>

--- a/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
+++ b/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3AF945-792E-4216-9CED-A7810B562435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{486CD00E-9D0F-499D-97E4-70788A5577CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -4451,10 +4451,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Si1-King1.jpg</t>
-  </si>
-  <si>
     <t>【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iu1-Iu1-Lok4-Bing5.jpg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6822,7 +6823,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="6" spans="2:4">
@@ -6838,7 +6839,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D7" s="47"/>
     </row>

--- a/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
+++ b/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{486CD00E-9D0F-499D-97E4-70788A5577CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{103C102B-9689-4ED8-A9C4-0E93E031541B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="195" yWindow="2595" windowWidth="28800" windowHeight="11295" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>

--- a/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
+++ b/output7/【河洛文讀注音-注音二式】《詩經．小雅．鹿鳴》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{103C102B-9689-4ED8-A9C4-0E93E031541B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C29F13C-AD23-4BE0-86EB-4DB5C5321161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="195" yWindow="2595" windowWidth="28800" windowHeight="11295" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="105" yWindow="2595" windowWidth="28695" windowHeight="11295" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
